--- a/Labs/7.AWS_Architecture_Lab/AWS_Team_Allocations.xlsx
+++ b/Labs/7.AWS_Architecture_Lab/AWS_Team_Allocations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Labs\7.AWS_Architecture_Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF93649-5F19-4C51-868D-0B88E3E76949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82882938-8F85-4EFA-BBC8-4CEE4816B78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS_DEV_Team1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
   <si>
     <t>Serial No.</t>
   </si>
@@ -141,13 +141,31 @@
   </si>
   <si>
     <t>Abhinav Singh</t>
+  </si>
+  <si>
+    <t>Gowrisankar Ravichandran</t>
+  </si>
+  <si>
+    <t>Did not participate</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Architecture diagram is primitive. Redo to include clear service boundaries - VPC, public and private subnets etc.</t>
+  </si>
+  <si>
+    <t>Class and Sequence diagrams are unclear. Redo according to samples.</t>
+  </si>
+  <si>
+    <t>Remove API Gateway from QA document.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,8 +181,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,6 +198,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -190,14 +232,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,23 +525,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -504,24 +556,33 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -529,7 +590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -537,15 +598,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
   </sheetData>
@@ -618,7 +682,7 @@
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -653,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -688,15 +752,15 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>29</v>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -857,7 +921,7 @@
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>36</v>
       </c>
     </row>

--- a/Labs/7.AWS_Architecture_Lab/AWS_Team_Allocations.xlsx
+++ b/Labs/7.AWS_Architecture_Lab/AWS_Team_Allocations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Labs\7.AWS_Architecture_Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82882938-8F85-4EFA-BBC8-4CEE4816B78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E9A0F2-2427-4A25-86A8-2DFD6258FC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS_DEV_Team1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
   <si>
     <t>Serial No.</t>
   </si>
@@ -146,19 +146,42 @@
     <t>Gowrisankar Ravichandran</t>
   </si>
   <si>
-    <t>Did not participate</t>
-  </si>
-  <si>
     <t>Review</t>
   </si>
   <si>
     <t>Architecture diagram is primitive. Redo to include clear service boundaries - VPC, public and private subnets etc.</t>
   </si>
   <si>
-    <t>Class and Sequence diagrams are unclear. Redo according to samples.</t>
-  </si>
-  <si>
     <t>Remove API Gateway from QA document.</t>
+  </si>
+  <si>
+    <t>Class and Sequence diagrams are unclear. Redo according to samples. Use Draw.io not Chat GPT.</t>
+  </si>
+  <si>
+    <t>Single AZ is mentioned along with multi AZ elsewhere.</t>
+  </si>
+  <si>
+    <t>Architecture diagram is primitive. React App/ NAT is missing. Redo to include clear service boundaries - VPC, public and private subnets etc.</t>
+  </si>
+  <si>
+    <t>Complete Specification document.</t>
+  </si>
+  <si>
+    <t>AWS architecture diagram should clearly show:</t>
+  </si>
+  <si>
+    <t>Frontend &amp; Edge: S3 + CloudFront
+Ingress: ALB with WAF
+Compute: EKS Cluster hosting microservices
+Data: RDS and DynamoDB
+Security: Secrets Manager
+Async Processing: SQS queues for payments and reporting</t>
+  </si>
+  <si>
+    <t>Add Sequence diagram</t>
+  </si>
+  <si>
+    <t>Did not contribute</t>
   </si>
 </sst>
 </file>
@@ -188,7 +211,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,12 +221,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -232,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -240,11 +257,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,7 +569,7 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -556,18 +582,18 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D2" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -578,8 +604,8 @@
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>42</v>
+      <c r="D4" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -602,11 +628,11 @@
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -619,42 +645,53 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72B0D5C8-4554-4889-8DEC-C5546F89AE7C}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -662,7 +699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -670,23 +707,26 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
   </sheetData>
@@ -759,7 +799,7 @@
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -773,42 +813,56 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD705E90-94E2-437E-8A40-0C0428628BF6}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -816,15 +870,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -832,7 +889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -840,7 +897,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
   </sheetData>
@@ -855,7 +912,7 @@
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -932,23 +989,28 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66997CB1-9B0E-4B45-8E51-D6EE1FDCB411}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="38.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -958,24 +1020,33 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -983,13 +1054,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
   </sheetData>
